--- a/artfynd/S 1405-2024 artfynd.xlsx
+++ b/artfynd/S 1405-2024 artfynd.xlsx
@@ -1434,7 +1434,7 @@
         <v>136439581</v>
       </c>
       <c r="B9" t="n">
-        <v>110322</v>
+        <v>110325</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>136439583</v>
       </c>
       <c r="B10" t="n">
-        <v>110322</v>
+        <v>110325</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>136439589</v>
       </c>
       <c r="B11" t="n">
-        <v>110322</v>
+        <v>110325</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>136439595</v>
       </c>
       <c r="B12" t="n">
-        <v>110322</v>
+        <v>110325</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>136439597</v>
       </c>
       <c r="B13" t="n">
-        <v>110322</v>
+        <v>110325</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>136439599</v>
       </c>
       <c r="B14" t="n">
-        <v>110322</v>
+        <v>110325</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>136439601</v>
       </c>
       <c r="B15" t="n">
-        <v>102790</v>
+        <v>102793</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/S 1405-2024 artfynd.xlsx
+++ b/artfynd/S 1405-2024 artfynd.xlsx
@@ -1434,7 +1434,7 @@
         <v>136439581</v>
       </c>
       <c r="B9" t="n">
-        <v>110325</v>
+        <v>110326</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>136439583</v>
       </c>
       <c r="B10" t="n">
-        <v>110325</v>
+        <v>110326</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>136439589</v>
       </c>
       <c r="B11" t="n">
-        <v>110325</v>
+        <v>110326</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>136439595</v>
       </c>
       <c r="B12" t="n">
-        <v>110325</v>
+        <v>110326</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>136439597</v>
       </c>
       <c r="B13" t="n">
-        <v>110325</v>
+        <v>110326</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>136439599</v>
       </c>
       <c r="B14" t="n">
-        <v>110325</v>
+        <v>110326</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>136439601</v>
       </c>
       <c r="B15" t="n">
-        <v>102793</v>
+        <v>102794</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/S 1405-2024 artfynd.xlsx
+++ b/artfynd/S 1405-2024 artfynd.xlsx
@@ -1434,7 +1434,7 @@
         <v>136439581</v>
       </c>
       <c r="B9" t="n">
-        <v>110326</v>
+        <v>110331</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>136439583</v>
       </c>
       <c r="B10" t="n">
-        <v>110326</v>
+        <v>110331</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>136439589</v>
       </c>
       <c r="B11" t="n">
-        <v>110326</v>
+        <v>110331</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>136439595</v>
       </c>
       <c r="B12" t="n">
-        <v>110326</v>
+        <v>110331</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>136439597</v>
       </c>
       <c r="B13" t="n">
-        <v>110326</v>
+        <v>110331</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>136439599</v>
       </c>
       <c r="B14" t="n">
-        <v>110326</v>
+        <v>110331</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>136439601</v>
       </c>
       <c r="B15" t="n">
-        <v>102794</v>
+        <v>102799</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/S 1405-2024 artfynd.xlsx
+++ b/artfynd/S 1405-2024 artfynd.xlsx
@@ -1434,7 +1434,7 @@
         <v>136439581</v>
       </c>
       <c r="B9" t="n">
-        <v>110331</v>
+        <v>110333</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>136439583</v>
       </c>
       <c r="B10" t="n">
-        <v>110331</v>
+        <v>110333</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>136439589</v>
       </c>
       <c r="B11" t="n">
-        <v>110331</v>
+        <v>110333</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>136439595</v>
       </c>
       <c r="B12" t="n">
-        <v>110331</v>
+        <v>110333</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>136439597</v>
       </c>
       <c r="B13" t="n">
-        <v>110331</v>
+        <v>110333</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>136439599</v>
       </c>
       <c r="B14" t="n">
-        <v>110331</v>
+        <v>110333</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>136439601</v>
       </c>
       <c r="B15" t="n">
-        <v>102799</v>
+        <v>102801</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/S 1405-2024 artfynd.xlsx
+++ b/artfynd/S 1405-2024 artfynd.xlsx
@@ -1434,7 +1434,7 @@
         <v>136439581</v>
       </c>
       <c r="B9" t="n">
-        <v>110333</v>
+        <v>110339</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>136439583</v>
       </c>
       <c r="B10" t="n">
-        <v>110333</v>
+        <v>110339</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>136439589</v>
       </c>
       <c r="B11" t="n">
-        <v>110333</v>
+        <v>110339</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>136439595</v>
       </c>
       <c r="B12" t="n">
-        <v>110333</v>
+        <v>110339</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>136439597</v>
       </c>
       <c r="B13" t="n">
-        <v>110333</v>
+        <v>110339</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>136439599</v>
       </c>
       <c r="B14" t="n">
-        <v>110333</v>
+        <v>110339</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>136439601</v>
       </c>
       <c r="B15" t="n">
-        <v>102801</v>
+        <v>102807</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/S 1405-2024 artfynd.xlsx
+++ b/artfynd/S 1405-2024 artfynd.xlsx
@@ -1434,7 +1434,7 @@
         <v>136439581</v>
       </c>
       <c r="B9" t="n">
-        <v>110339</v>
+        <v>110341</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>136439583</v>
       </c>
       <c r="B10" t="n">
-        <v>110339</v>
+        <v>110341</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>136439589</v>
       </c>
       <c r="B11" t="n">
-        <v>110339</v>
+        <v>110341</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>136439595</v>
       </c>
       <c r="B12" t="n">
-        <v>110339</v>
+        <v>110341</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>136439597</v>
       </c>
       <c r="B13" t="n">
-        <v>110339</v>
+        <v>110341</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>136439599</v>
       </c>
       <c r="B14" t="n">
-        <v>110339</v>
+        <v>110341</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>136439601</v>
       </c>
       <c r="B15" t="n">
-        <v>102807</v>
+        <v>102809</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/S 1405-2024 artfynd.xlsx
+++ b/artfynd/S 1405-2024 artfynd.xlsx
@@ -1434,7 +1434,7 @@
         <v>136439581</v>
       </c>
       <c r="B9" t="n">
-        <v>110341</v>
+        <v>110342</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>136439583</v>
       </c>
       <c r="B10" t="n">
-        <v>110341</v>
+        <v>110342</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>136439589</v>
       </c>
       <c r="B11" t="n">
-        <v>110341</v>
+        <v>110342</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>136439595</v>
       </c>
       <c r="B12" t="n">
-        <v>110341</v>
+        <v>110342</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>136439597</v>
       </c>
       <c r="B13" t="n">
-        <v>110341</v>
+        <v>110342</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>136439599</v>
       </c>
       <c r="B14" t="n">
-        <v>110341</v>
+        <v>110342</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>136439601</v>
       </c>
       <c r="B15" t="n">
-        <v>102809</v>
+        <v>102810</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
